--- a/data/trans_orig/P13A_1_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P13A_1_R-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cefaleas crónicas (15 días o más al mes durante más de 3 meses) en 2023</t>
+          <t>Población con cefaleas crónicas (15 días o más al mes durante más de 3 meses) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5430</t>
+          <t>5595</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16101</t>
+          <t>16416</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33433</t>
+          <t>33416</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65152</t>
+          <t>63124</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42123</t>
+          <t>41280</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73912</t>
+          <t>71510</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>498496</t>
+          <t>498181</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>509167</t>
+          <t>509002</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>685995</t>
+          <t>688023</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>717714</t>
+          <t>717731</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1191832</t>
+          <t>1194234</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1223621</t>
+          <t>1224464</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15778</t>
+          <t>14825</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39038</t>
+          <t>38090</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60081</t>
+          <t>57787</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>101318</t>
+          <t>102092</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81458</t>
+          <t>81287</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>128576</t>
+          <t>128549</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2240672</t>
+          <t>2241620</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2263932</t>
+          <t>2264885</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2128800</t>
+          <t>2128026</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2170037</t>
+          <t>2172331</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4381252</t>
+          <t>4381279</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4428370</t>
+          <t>4428541</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8290</t>
+          <t>9076</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13305</t>
+          <t>12691</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30456</t>
+          <t>28903</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15643</t>
+          <t>14749</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32573</t>
+          <t>31510</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>637706</t>
+          <t>636920</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>628265</t>
+          <t>629818</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>645416</t>
+          <t>646030</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1272144</t>
+          <t>1273207</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1289074</t>
+          <t>1289968</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26150</t>
+          <t>26768</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53199</t>
+          <t>51706</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>117053</t>
+          <t>116173</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>173463</t>
+          <t>172154</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>151023</t>
+          <t>151506</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>211515</t>
+          <t>213357</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3387105</t>
+          <t>3388598</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3414154</t>
+          <t>3413536</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3466522</t>
+          <t>3467831</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3522932</t>
+          <t>3523812</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6868774</t>
+          <t>6866932</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6929266</t>
+          <t>6928783</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P13A_1_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P13A_1_R-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>10195</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16416</t>
+          <t>18369</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>43071</t>
+          <t>42998</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33416</t>
+          <t>32908</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63124</t>
+          <t>53372</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>52757</t>
+          <t>53192</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41280</t>
+          <t>42131</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>71510</t>
+          <t>65409</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>504911</t>
+          <t>567992</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>498181</t>
+          <t>559818</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>509002</t>
+          <t>572445</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>708076</t>
+          <t>774434</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>688023</t>
+          <t>764060</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>784524</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1212987</t>
+          <t>1342427</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1194234</t>
+          <t>1330210</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1224464</t>
+          <t>1353488</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,98%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514597</t>
+          <t>578187</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514597</t>
+          <t>578187</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514597</t>
+          <t>578187</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>751147</t>
+          <t>817432</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>751147</t>
+          <t>817432</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>751147</t>
+          <t>817432</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1265744</t>
+          <t>1395619</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1265744</t>
+          <t>1395619</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1265744</t>
+          <t>1395619</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>27327</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14825</t>
+          <t>17768</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38090</t>
+          <t>41138</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>79975</t>
+          <t>87561</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57787</t>
+          <t>73419</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>102092</t>
+          <t>107075</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>105347</t>
+          <t>114888</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81287</t>
+          <t>96167</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>128549</t>
+          <t>137873</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2254338</t>
+          <t>2191565</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2241620</t>
+          <t>2177754</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2264885</t>
+          <t>2201124</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2150143</t>
+          <t>2072776</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2128026</t>
+          <t>2053262</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2172331</t>
+          <t>2086918</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4404481</t>
+          <t>4264341</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4381279</t>
+          <t>4241356</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4428541</t>
+          <t>4283062</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2279710</t>
+          <t>2218892</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2279710</t>
+          <t>2218892</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2279710</t>
+          <t>2218892</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2230118</t>
+          <t>2160337</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2230118</t>
+          <t>2160337</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2230118</t>
+          <t>2160337</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4509828</t>
+          <t>4379229</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4509828</t>
+          <t>4379229</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4509828</t>
+          <t>4379229</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2386</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9076</t>
+          <t>7312</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>19857</t>
+          <t>23854</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12691</t>
+          <t>15960</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28903</t>
+          <t>35432</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>22193</t>
+          <t>26240</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14749</t>
+          <t>17672</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31510</t>
+          <t>37316</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>643660</t>
+          <t>708589</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>636920</t>
+          <t>703663</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>645996</t>
+          <t>710975</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>638864</t>
+          <t>708551</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>629818</t>
+          <t>696973</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>646030</t>
+          <t>716445</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1282524</t>
+          <t>1417140</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1273207</t>
+          <t>1406064</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1289968</t>
+          <t>1425708</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>645996</t>
+          <t>710975</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>645996</t>
+          <t>710975</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>645996</t>
+          <t>710975</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>658721</t>
+          <t>732405</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>658721</t>
+          <t>732405</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>658721</t>
+          <t>732405</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1304717</t>
+          <t>1443380</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1304717</t>
+          <t>1443380</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1304717</t>
+          <t>1443380</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26768</t>
+          <t>28423</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51706</t>
+          <t>54866</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>142903</t>
+          <t>154412</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>116173</t>
+          <t>135656</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>172154</t>
+          <t>181890</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>180297</t>
+          <t>194320</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>151506</t>
+          <t>168556</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>213357</t>
+          <t>219230</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3402911</t>
+          <t>3468146</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3388598</t>
+          <t>3453188</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3413536</t>
+          <t>3479631</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3497082</t>
+          <t>3555762</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3467831</t>
+          <t>3528284</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3523812</t>
+          <t>3574518</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6899992</t>
+          <t>7023908</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6866932</t>
+          <t>6998998</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6928783</t>
+          <t>7049672</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3440304</t>
+          <t>3508054</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3440304</t>
+          <t>3508054</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3440304</t>
+          <t>3508054</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3639985</t>
+          <t>3710174</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3639985</t>
+          <t>3710174</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3639985</t>
+          <t>3710174</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7080289</t>
+          <t>7218228</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7080289</t>
+          <t>7218228</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7080289</t>
+          <t>7218228</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
